--- a/outputs/daily/hr_rankings_2026-08-20_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-20_remaining.xlsx
@@ -1369,7 +1369,7 @@
         <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>51.3</v>
+        <v>49.9</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2737,7 +2737,7 @@
         <v>60</v>
       </c>
       <c r="U9" t="n">
-        <v>40.9</v>
+        <v>40.1</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>56.6</v>
+        <v>56.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>78</v>
       </c>
       <c r="U10" t="n">
-        <v>16.6</v>
+        <v>15.3</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5404,7 +5404,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>52.8</v>
+        <v>52.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>68.7</v>
+        <v>63.7</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -5680,7 +5680,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>50</v>
       </c>
       <c r="U20" t="n">
-        <v>54.7</v>
+        <v>53.3</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -5907,24 +5907,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>669394</t>
+          <t>687263</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jake Burger</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>2026-08-22T00:15:00Z</t>
@@ -5937,17 +5937,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Reid Detmers</t>
+          <t>MacKenzie Gore</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>672282</t>
+          <t>669022</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -5974,22 +5974,22 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>48.5</v>
+        <v>46.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>40.4</v>
+        <v>46.5</v>
       </c>
       <c r="R21" t="n">
         <v>27.6</v>
       </c>
       <c r="S21" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T21" t="n">
         <v>78</v>
       </c>
       <c r="U21" t="n">
-        <v>56.2</v>
+        <v>46.5</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -6045,27 +6045,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 13.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 18.6 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -6075,97 +6075,97 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>89.74</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>102.6757</t>
+          <t>100.102</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4227</t>
+          <t>0.4166</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.1872</t>
+          <t>0.2027</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3086</t>
+          <t>0.3097</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>75.37</t>
+          <t>71.26</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>58.14</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>41.88</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>34.96</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1844</t>
+          <t>0.1946</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>42.63</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>90.03</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>0.3891</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1439</t>
+          <t>0.1509</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr"/>
@@ -6496,7 +6496,7 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>60</v>
       </c>
       <c r="U23" t="n">
-        <v>59.1</v>
+        <v>57.6</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -6699,27 +6699,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>621566</t>
+          <t>669394</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Matt Olson</t>
+          <t>Jake Burger</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-21T20:10:00Z</t>
+          <t>2026-08-22T00:15:00Z</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -6734,21 +6734,21 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Reid Detmers</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>672282</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>52.2</v>
+        <v>52.4</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6766,10 +6766,10 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>67.5</v>
+        <v>48.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>17.4</v>
+        <v>40.4</v>
       </c>
       <c r="R24" t="n">
         <v>27.6</v>
@@ -6778,10 +6778,10 @@
         <v>92.09999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U24" t="n">
-        <v>30.3</v>
+        <v>53.3</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -6837,134 +6837,134 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.6% barrel, 11.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 13.7 HR allowed</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>50.92</t>
+          <t>47.17</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>92.81</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>103.8576</t>
+          <t>102.6757</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>0.5137</t>
+          <t>0.4227</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>0.2643</t>
+          <t>0.1872</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>0.3628</t>
+          <t>0.3086</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.37</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>48.03</t>
+          <t>58.14</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>41.88</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>32.71</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>0.2617</t>
+          <t>0.1844</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>34.77</t>
+          <t>39.58</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>90.03</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>0.2747</t>
+          <t>0.363</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
-          <t>0.0989</t>
+          <t>0.1439</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>28.69</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr"/>
       <c r="BH24" t="inlineStr"/>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr"/>
@@ -6975,27 +6975,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>621566</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Matt Olson</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-22T00:40:00Z</t>
+          <t>2026-08-21T20:10:00Z</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Tanner Gordon</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>685299</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -7024,7 +7024,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -7038,26 +7038,26 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>30.3</v>
+        <v>67.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>64.09999999999999</v>
+        <v>17.4</v>
       </c>
       <c r="R25" t="n">
-        <v>38.7</v>
+        <v>27.6</v>
       </c>
       <c r="S25" t="n">
         <v>92.09999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U25" t="n">
-        <v>25.8</v>
+        <v>30.3</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -7113,134 +7113,134 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 0 HR</t>
+          <t>Last 7 games: 5/25, 1 HR</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 11.2% barrel, 15.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.6% barrel, 11.5 HR allowed</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>50.92</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>89.25</t>
+          <t>92.81</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>99.7032</t>
+          <t>103.8576</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>0.4334</t>
+          <t>0.5137</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>0.1494</t>
+          <t>0.2643</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>0.3628</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>70.34</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>13.47</t>
+          <t>48.03</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>32.71</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.1682</t>
+          <t>0.2617</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>34.77</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>91.15</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>0.4985</t>
+          <t>0.2747</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
-          <t>0.2244</t>
+          <t>0.0989</t>
         </is>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>33.53</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr"/>
       <c r="BH25" t="inlineStr"/>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr"/>
@@ -7251,27 +7251,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>671277</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Luis Garcia</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-21T23:05:00Z</t>
+          <t>2026-08-22T00:40:00Z</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7281,14 +7281,26 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Tanner Gordon</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>685299</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L26" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7302,26 +7314,26 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>49</v>
+        <v>30.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>41.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="R26" t="n">
-        <v>38.2</v>
+        <v>38.7</v>
       </c>
       <c r="S26" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U26" t="n">
-        <v>43.2</v>
+        <v>25.8</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -7335,7 +7347,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -7360,7 +7372,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr"/>
@@ -7377,110 +7389,134 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 1 HR</t>
+          <t>Last 7 games: 7/24, 0 HR</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 11.2% barrel, 15.3 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>91.18</t>
+          <t>89.25</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>101.7652</t>
+          <t>99.7032</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.4847</t>
+          <t>0.4334</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.2023</t>
+          <t>0.1494</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.3432</t>
+          <t>0.349</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>70.34</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>13.47</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>40.52</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.2279</t>
-        </is>
-      </c>
-      <c r="BA26" t="inlineStr"/>
-      <c r="BB26" t="inlineStr"/>
-      <c r="BC26" t="inlineStr"/>
-      <c r="BD26" t="inlineStr"/>
-      <c r="BE26" t="inlineStr"/>
-      <c r="BF26" t="inlineStr"/>
+          <t>0.1682</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>11.22</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>43.93</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>91.15</t>
+        </is>
+      </c>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>0.4985</t>
+        </is>
+      </c>
+      <c r="BE26" t="inlineStr">
+        <is>
+          <t>0.2244</t>
+        </is>
+      </c>
+      <c r="BF26" t="inlineStr">
+        <is>
+          <t>33.53</t>
+        </is>
+      </c>
       <c r="BG26" t="inlineStr"/>
       <c r="BH26" t="inlineStr"/>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr"/>
@@ -7491,27 +7527,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>663886</t>
+          <t>671277</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tyler Stephenson</t>
+          <t>Luis Garcia</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-22T01:40:00Z</t>
+          <t>2026-08-21T23:05:00Z</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7524,23 +7560,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Eduardo Rodriguez</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>593958</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7554,26 +7578,26 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>51.8</v>
+        <v>49</v>
       </c>
       <c r="Q27" t="n">
-        <v>41.7</v>
+        <v>41.2</v>
       </c>
       <c r="R27" t="n">
-        <v>28.2</v>
+        <v>38.2</v>
       </c>
       <c r="S27" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="U27" t="n">
-        <v>18.3</v>
+        <v>43.2</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -7612,7 +7636,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr"/>
@@ -7629,27 +7653,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/20, 1 HR</t>
+          <t>Last 7 games: 8/28, 1 HR</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 17.3 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -7659,104 +7683,80 @@
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>13.17</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>47.03</t>
+          <t>45.94</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>90.92</t>
+          <t>91.18</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>100.5243</t>
+          <t>101.7652</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>0.4459</t>
+          <t>0.4847</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>0.2075</t>
+          <t>0.2023</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>0.3347</t>
+          <t>0.3432</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>70.52</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>36.52</t>
+          <t>40.52</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>32.94</t>
+          <t>22.61</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.1746</t>
-        </is>
-      </c>
-      <c r="BA27" t="inlineStr">
-        <is>
-          <t>8.27</t>
-        </is>
-      </c>
-      <c r="BB27" t="inlineStr">
-        <is>
-          <t>35.2</t>
-        </is>
-      </c>
-      <c r="BC27" t="inlineStr">
-        <is>
-          <t>87.99</t>
-        </is>
-      </c>
-      <c r="BD27" t="inlineStr">
-        <is>
-          <t>0.4391</t>
-        </is>
-      </c>
-      <c r="BE27" t="inlineStr">
-        <is>
-          <t>0.1755</t>
-        </is>
-      </c>
-      <c r="BF27" t="inlineStr">
-        <is>
-          <t>27.4</t>
-        </is>
-      </c>
+          <t>0.2279</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
       <c r="BG27" t="inlineStr"/>
       <c r="BH27" t="inlineStr"/>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr"/>
@@ -7767,12 +7767,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>682829</t>
+          <t>663886</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Tyler Stephenson</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -7816,7 +7816,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>51.4</v>
+        <v>51.9</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -7834,22 +7834,22 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>55.2</v>
+        <v>51.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>39.8</v>
+        <v>41.7</v>
       </c>
       <c r="R28" t="n">
         <v>28.2</v>
       </c>
       <c r="S28" t="n">
-        <v>88.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T28" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U28" t="n">
-        <v>5.1</v>
+        <v>18.3</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -7905,97 +7905,97 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 1/20, 1 HR</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.3% barrel, 17.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 17.3 HR allowed</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>13.17</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>47.03</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>93.03</t>
+          <t>90.92</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>104.0011</t>
+          <t>100.5243</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>0.4541</t>
+          <t>0.4459</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>0.1919</t>
+          <t>0.2075</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>0.3465</t>
+          <t>0.3347</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>75.38</t>
+          <t>70.52</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>53.84</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>34.12</t>
+          <t>36.52</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>32.94</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.1991</t>
+          <t>0.1746</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
@@ -8043,27 +8043,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>682829</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-21T23:15:00Z</t>
+          <t>2026-08-22T01:40:00Z</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8073,17 +8073,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Trevor Rogers</t>
+          <t>Eduardo Rodriguez</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>669432</t>
+          <t>593958</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8106,26 +8106,26 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>41.9</v>
+        <v>55.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>37.9</v>
+        <v>39.8</v>
       </c>
       <c r="R29" t="n">
-        <v>32.1</v>
+        <v>28.2</v>
       </c>
       <c r="S29" t="n">
-        <v>90.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T29" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U29" t="n">
-        <v>77.59999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -8181,134 +8181,134 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 10.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.3% barrel, 17.3 HR allowed</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>93.03</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>103.2475</t>
+          <t>104.0011</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>0.4569</t>
+          <t>0.4541</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.1919</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>0.3593</t>
+          <t>0.3465</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>73.64</t>
+          <t>75.38</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>37.86</t>
+          <t>53.84</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>23.04</t>
+          <t>34.12</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.1722</t>
+          <t>0.1991</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>87.99</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>0.3921</t>
+          <t>0.4391</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
-          <t>0.1496</t>
+          <t>0.1755</t>
         </is>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="BG29" t="inlineStr"/>
       <c r="BH29" t="inlineStr"/>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr"/>
@@ -8319,27 +8319,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>687263</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-22T00:15:00Z</t>
+          <t>2026-08-21T23:15:00Z</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>MacKenzie Gore</t>
+          <t>Trevor Rogers</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>669022</t>
+          <t>669432</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -8368,7 +8368,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8382,17 +8382,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>46.3</v>
+        <v>41.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>46.5</v>
+        <v>37.9</v>
       </c>
       <c r="R30" t="n">
-        <v>27.6</v>
+        <v>32.1</v>
       </c>
       <c r="S30" t="n">
         <v>90.40000000000001</v>
@@ -8401,7 +8401,7 @@
         <v>78</v>
       </c>
       <c r="U30" t="n">
-        <v>19.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -8457,27 +8457,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 18.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 10.9 HR allowed</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -8487,104 +8487,104 @@
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>89.74</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>100.102</t>
+          <t>103.2475</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>0.4166</t>
+          <t>0.4569</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>0.2027</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.3593</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>71.26</t>
+          <t>73.64</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>37.86</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>23.04</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>34.96</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.1946</t>
+          <t>0.1722</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>42.63</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>0.3891</t>
+          <t>0.3921</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>0.1509</t>
+          <t>0.1496</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr"/>
       <c r="BH30" t="inlineStr"/>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr"/>
@@ -8953,7 +8953,7 @@
         <v>80</v>
       </c>
       <c r="U32" t="n">
-        <v>20.8</v>
+        <v>19.9</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/22, 1 HR</t>
+          <t>Last 7 games: 3/23, 1 HR</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
@@ -11319,27 +11319,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>677588</t>
+          <t>676475</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jose Tena</t>
+          <t>Alec Burleson</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-21T23:10:00Z</t>
+          <t>2026-08-21T22:40:00Z</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -11349,26 +11349,26 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Ryan Gusto</t>
+          <t>Jesús Luzardo</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>687473</t>
+          <t>666200</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -11382,26 +11382,26 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>35.3</v>
+        <v>54.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>48.6</v>
+        <v>21.4</v>
       </c>
       <c r="R41" t="n">
-        <v>21.5</v>
+        <v>34.3</v>
       </c>
       <c r="S41" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T41" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U41" t="n">
-        <v>56.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -11477,7 +11477,7 @@
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.1% barrel, 13.2 HR allowed</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -11487,104 +11487,104 @@
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>90.81</t>
+          <t>91.77</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>101.954</t>
+          <t>102.014</t>
         </is>
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>0.5207</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>0.1371</t>
+          <t>0.2298</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr">
         <is>
-          <t>0.3083</t>
+          <t>0.3744</t>
         </is>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>72.94</t>
+          <t>73.14</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>30.81</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>27.61</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>0.1484</t>
+          <t>0.1921</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>87.59</t>
         </is>
       </c>
       <c r="BD41" t="inlineStr">
         <is>
-          <t>0.4257</t>
+          <t>0.3193</t>
         </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
-          <t>0.1669</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="BF41" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="BG41" t="inlineStr"/>
       <c r="BH41" t="inlineStr"/>
       <c r="BI41" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ41" t="inlineStr"/>
@@ -11595,27 +11595,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>676475</t>
+          <t>677588</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alec Burleson</t>
+          <t>Jose Tena</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-21T22:40:00Z</t>
+          <t>2026-08-21T23:10:00Z</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -11625,22 +11625,22 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Jesús Luzardo</t>
+          <t>Ryan Gusto</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>666200</t>
+          <t>687473</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -11658,26 +11658,26 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>54.1</v>
+        <v>35.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>21.4</v>
+        <v>48.6</v>
       </c>
       <c r="R42" t="n">
-        <v>34.3</v>
+        <v>21.5</v>
       </c>
       <c r="S42" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T42" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U42" t="n">
-        <v>70.40000000000001</v>
+        <v>53.3</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -11733,12 +11733,12 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.1% barrel, 13.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -11763,104 +11763,104 @@
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>91.77</t>
+          <t>90.81</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>102.014</t>
+          <t>101.954</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>0.5207</t>
+          <t>0.378</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>0.2298</t>
+          <t>0.1371</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>0.3744</t>
+          <t>0.3083</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>73.14</t>
+          <t>72.94</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>33.18</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>30.81</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>27.61</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>0.1921</t>
+          <t>0.1484</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>87.59</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="BD42" t="inlineStr">
         <is>
-          <t>0.3193</t>
+          <t>0.4257</t>
         </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.1669</t>
         </is>
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="BG42" t="inlineStr"/>
       <c r="BH42" t="inlineStr"/>
       <c r="BI42" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ42" t="inlineStr"/>
@@ -11920,7 +11920,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>80</v>
       </c>
       <c r="U43" t="n">
-        <v>54.3</v>
+        <v>52.3</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -12024,7 +12024,7 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Contact streak: 9/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
@@ -12147,27 +12147,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>694671</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wyatt Langford</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-22T00:15:00Z</t>
+          <t>2026-08-21T20:10:00Z</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -12177,17 +12177,17 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Reid Detmers</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>672282</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -12196,7 +12196,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -12210,26 +12210,26 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>40.8</v>
+        <v>51.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>40.4</v>
+        <v>22</v>
       </c>
       <c r="R44" t="n">
         <v>27.6</v>
       </c>
       <c r="S44" t="n">
-        <v>88.7</v>
+        <v>95.5</v>
       </c>
       <c r="T44" t="n">
         <v>78</v>
       </c>
       <c r="U44" t="n">
-        <v>36.3</v>
+        <v>33.7</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -12285,27 +12285,27 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Contact streak: 10/29 over last 7 games</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 13.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.8% barrel, 8.9 HR allowed</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
@@ -12315,104 +12315,104 @@
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>45.66</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>90.21</t>
+          <t>91.19</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>100.9254</t>
+          <t>102.0101</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>0.4137</t>
+          <t>0.4596</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>0.1764</t>
+          <t>0.2056</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr">
         <is>
-          <t>0.3194</t>
+          <t>0.3287</t>
         </is>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>30.73</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>0.2012</t>
+          <t>0.1916</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>34.77</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>90.03</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD44" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>0.327</t>
         </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
-          <t>0.1439</t>
+          <t>0.1094</t>
         </is>
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>25.69</t>
         </is>
       </c>
       <c r="BG44" t="inlineStr"/>
       <c r="BH44" t="inlineStr"/>
       <c r="BI44" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ44" t="inlineStr"/>
@@ -12423,27 +12423,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>694671</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Wyatt Langford</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-21T20:10:00Z</t>
+          <t>2026-08-22T00:15:00Z</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -12453,17 +12453,17 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Reid Detmers</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>672282</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -12486,26 +12486,26 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>51.5</v>
+        <v>40.8</v>
       </c>
       <c r="Q45" t="n">
-        <v>22</v>
+        <v>40.4</v>
       </c>
       <c r="R45" t="n">
         <v>27.6</v>
       </c>
       <c r="S45" t="n">
-        <v>95.5</v>
+        <v>88.7</v>
       </c>
       <c r="T45" t="n">
         <v>78</v>
       </c>
       <c r="U45" t="n">
-        <v>33.7</v>
+        <v>34.9</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -12561,27 +12561,27 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Contact streak: 10/29 over last 7 games</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.8% barrel, 8.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 13.7 HR allowed</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
@@ -12591,104 +12591,104 @@
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>45.66</t>
+          <t>42.03</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>91.19</t>
+          <t>90.21</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>102.0101</t>
+          <t>100.9254</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>0.4596</t>
+          <t>0.4137</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>0.2056</t>
+          <t>0.1764</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>0.3287</t>
+          <t>0.3194</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>30.73</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>0.1916</t>
+          <t>0.2012</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>34.77</t>
+          <t>39.58</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>90.03</t>
         </is>
       </c>
       <c r="BD45" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>0.363</t>
         </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
-          <t>0.1094</t>
+          <t>0.1439</t>
         </is>
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>25.69</t>
+          <t>28.69</t>
         </is>
       </c>
       <c r="BG45" t="inlineStr"/>
       <c r="BH45" t="inlineStr"/>
       <c r="BI45" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ45" t="inlineStr"/>
@@ -13300,7 +13300,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         <v>50</v>
       </c>
       <c r="U48" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Last 7 games: 4/27, 0 HR</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
@@ -15975,27 +15975,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>695734</t>
+          <t>703607</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Daylen Lile</t>
+          <t>Henry Bolte</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-21T23:10:00Z</t>
+          <t>2026-08-22T00:10:00Z</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -16010,12 +16010,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Ryan Gusto</t>
+          <t>Hayden Wesneski</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>687473</t>
+          <t>669713</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -16038,26 +16038,26 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>32.9</v>
+        <v>35.6</v>
       </c>
       <c r="Q58" t="n">
-        <v>48.6</v>
+        <v>42.1</v>
       </c>
       <c r="R58" t="n">
-        <v>21.5</v>
+        <v>27.6</v>
       </c>
       <c r="S58" t="n">
         <v>88.7</v>
       </c>
       <c r="T58" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U58" t="n">
-        <v>5.1</v>
+        <v>53.6</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr"/>
@@ -16113,27 +16113,27 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Contact streak: 11/31 over last 7 games</t>
         </is>
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 3.5 HR allowed</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
@@ -16143,104 +16143,104 @@
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>88.62</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>98.8018</t>
+          <t>104.3344</t>
         </is>
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>0.4294</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.306</t>
         </is>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>0.1731</t>
+          <t>0.101</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>42.03</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>89.56</t>
         </is>
       </c>
       <c r="BD58" t="inlineStr">
         <is>
-          <t>0.4257</t>
+          <t>0.4227</t>
         </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
-          <t>0.1669</t>
+          <t>0.1627</t>
         </is>
       </c>
       <c r="BF58" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="BG58" t="inlineStr"/>
       <c r="BH58" t="inlineStr"/>
       <c r="BI58" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ58" t="inlineStr"/>
@@ -16251,27 +16251,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>703607</t>
+          <t>695734</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Henry Bolte</t>
+          <t>Daylen Lile</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-22T00:10:00Z</t>
+          <t>2026-08-21T23:10:00Z</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -16286,12 +16286,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Hayden Wesneski</t>
+          <t>Ryan Gusto</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>669713</t>
+          <t>687473</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -16300,7 +16300,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -16314,26 +16314,26 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>35.6</v>
+        <v>32.9</v>
       </c>
       <c r="Q59" t="n">
-        <v>42.1</v>
+        <v>48.6</v>
       </c>
       <c r="R59" t="n">
-        <v>27.6</v>
+        <v>21.5</v>
       </c>
       <c r="S59" t="n">
         <v>88.7</v>
       </c>
       <c r="T59" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U59" t="n">
-        <v>53.6</v>
+        <v>3.4</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr"/>
@@ -16389,27 +16389,27 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Contact streak: 11/31 over last 7 games</t>
+          <t>Last 7 games: 4/28, 0 HR</t>
         </is>
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 3.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
@@ -16419,104 +16419,104 @@
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>37.93</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.62</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>104.3344</t>
+          <t>98.8018</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.4294</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>0.1731</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>89.56</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="BD59" t="inlineStr">
         <is>
-          <t>0.4227</t>
+          <t>0.4257</t>
         </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
-          <t>0.1627</t>
+          <t>0.1669</t>
         </is>
       </c>
       <c r="BF59" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="BG59" t="inlineStr"/>
       <c r="BH59" t="inlineStr"/>
       <c r="BI59" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ59" t="inlineStr"/>
@@ -18508,7 +18508,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>44.5</v>
+        <v>44.3</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>50</v>
       </c>
       <c r="U67" t="n">
-        <v>12</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -18612,7 +18612,7 @@
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/10, 0 HR</t>
+          <t>Last 7 games: 2/11, 0 HR</t>
         </is>
       </c>
       <c r="AL67" t="inlineStr">
@@ -19839,27 +19839,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>666139</t>
+          <t>671056</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Josh Lowe</t>
+          <t>Ivan Herrera</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-22T00:15:00Z</t>
+          <t>2026-08-21T22:40:00Z</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -19869,17 +19869,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>MacKenzie Gore</t>
+          <t>Jesús Luzardo</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>669022</t>
+          <t>666200</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -19888,7 +19888,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>43.4</v>
+        <v>43.2</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -19902,26 +19902,26 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P72" t="n">
         <v>34.9</v>
       </c>
       <c r="Q72" t="n">
-        <v>46.5</v>
+        <v>21.4</v>
       </c>
       <c r="R72" t="n">
-        <v>27.6</v>
+        <v>34.3</v>
       </c>
       <c r="S72" t="n">
-        <v>59.8</v>
+        <v>95.5</v>
       </c>
       <c r="T72" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U72" t="n">
-        <v>73.2</v>
+        <v>20.8</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
@@ -19977,7 +19977,7 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
@@ -19987,17 +19987,17 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/22, 1 HR</t>
         </is>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.3% barrel, 18.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.1% barrel, 13.2 HR allowed</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
@@ -20007,104 +20007,104 @@
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.39</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>89.94</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>99.3977</t>
+          <t>101.3943</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>0.414</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1558</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>0.2966</t>
+          <t>0.3465</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>73.59</t>
+          <t>73.88</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>19.38</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0.152</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>42.63</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>87.59</t>
         </is>
       </c>
       <c r="BD72" t="inlineStr">
         <is>
-          <t>0.3891</t>
+          <t>0.3193</t>
         </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
-          <t>0.1509</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="BF72" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="BG72" t="inlineStr"/>
       <c r="BH72" t="inlineStr"/>
       <c r="BI72" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ72" t="inlineStr"/>
@@ -20115,27 +20115,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>671056</t>
+          <t>666139</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ivan Herrera</t>
+          <t>Josh Lowe</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-21T22:40:00Z</t>
+          <t>2026-08-22T00:15:00Z</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -20145,17 +20145,17 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Jesús Luzardo</t>
+          <t>MacKenzie Gore</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>666200</t>
+          <t>669022</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -20164,7 +20164,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -20178,26 +20178,26 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P73" t="n">
         <v>34.9</v>
       </c>
       <c r="Q73" t="n">
-        <v>21.4</v>
+        <v>46.5</v>
       </c>
       <c r="R73" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S73" t="n">
-        <v>95.5</v>
+        <v>59.8</v>
       </c>
       <c r="T73" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U73" t="n">
-        <v>20.8</v>
+        <v>66.7</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
@@ -20253,27 +20253,27 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/22, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.1% barrel, 13.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.3% barrel, 18.6 HR allowed</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
@@ -20283,104 +20283,104 @@
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>89.94</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
         <is>
-          <t>101.3943</t>
+          <t>99.3977</t>
         </is>
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>0.414</t>
+          <t>0.391</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>0.1558</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr">
         <is>
-          <t>0.3465</t>
+          <t>0.2966</t>
         </is>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>73.88</t>
+          <t>73.59</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>19.38</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>0.153</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>42.63</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>87.59</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="BD73" t="inlineStr">
         <is>
-          <t>0.3193</t>
+          <t>0.3891</t>
         </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.1509</t>
         </is>
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BG73" t="inlineStr"/>
       <c r="BH73" t="inlineStr"/>
       <c r="BI73" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ73" t="inlineStr"/>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
@@ -21648,7 +21648,7 @@
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/19, 0 HR</t>
+          <t>Last 7 games: 1/21, 0 HR</t>
         </is>
       </c>
       <c r="AL78" t="inlineStr">
@@ -21771,27 +21771,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>686611</t>
+          <t>694208</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dylan Crews</t>
+          <t>Moises Ballesteros</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-21T23:10:00Z</t>
+          <t>2026-08-22T00:15:00Z</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -21801,26 +21801,26 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Ryan Gusto</t>
+          <t>MacKenzie Gore</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>687473</t>
+          <t>669022</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>42.2</v>
+        <v>42.4</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -21834,26 +21834,26 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>42.6</v>
+        <v>33</v>
       </c>
       <c r="Q79" t="n">
-        <v>48.6</v>
+        <v>46.5</v>
       </c>
       <c r="R79" t="n">
-        <v>21.5</v>
+        <v>27.6</v>
       </c>
       <c r="S79" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T79" t="n">
         <v>50</v>
       </c>
       <c r="U79" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
@@ -21909,12 +21909,12 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -21924,12 +21924,12 @@
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/18, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL79" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.9% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.3% barrel, 18.6 HR allowed</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
@@ -21939,104 +21939,104 @@
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>101.1127</t>
+          <t>100.8755</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>0.4147</t>
+          <t>0.3825</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>0.1415</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>0.3154</t>
+          <t>0.3116</t>
         </is>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>73.83</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>37.23</t>
+          <t>34.34</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>33.17</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>0.1461</t>
+          <t>0.134</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>42.63</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="BD79" t="inlineStr">
         <is>
-          <t>0.4257</t>
+          <t>0.3891</t>
         </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
-          <t>0.1669</t>
+          <t>0.1509</t>
         </is>
       </c>
       <c r="BF79" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BG79" t="inlineStr"/>
       <c r="BH79" t="inlineStr"/>
       <c r="BI79" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ79" t="inlineStr"/>
@@ -22047,27 +22047,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>694208</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Moises Ballesteros</t>
+          <t>Michael Harris</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-22T00:15:00Z</t>
+          <t>2026-08-21T20:10:00Z</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -22077,26 +22077,26 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>MacKenzie Gore</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>669022</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -22110,26 +22110,26 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>33</v>
+        <v>45.9</v>
       </c>
       <c r="Q80" t="n">
-        <v>46.5</v>
+        <v>17.4</v>
       </c>
       <c r="R80" t="n">
         <v>27.6</v>
       </c>
       <c r="S80" t="n">
-        <v>81.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T80" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U80" t="n">
-        <v>1.6</v>
+        <v>28.2</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
@@ -22185,12 +22185,12 @@
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">
@@ -22200,12 +22200,12 @@
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/23, 0 HR</t>
+          <t>Last 7 games: 8/26, 0 HR</t>
         </is>
       </c>
       <c r="AL80" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.3% barrel, 18.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.6% barrel, 11.5 HR allowed</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
@@ -22215,104 +22215,104 @@
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
         <is>
-          <t>100.8755</t>
+          <t>103.328</t>
         </is>
       </c>
       <c r="AR80" t="inlineStr">
         <is>
-          <t>0.3825</t>
+          <t>0.4653</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>0.1415</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr">
         <is>
-          <t>0.3116</t>
+          <t>0.3346</t>
         </is>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>34.34</t>
+          <t>47.68</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>36.22</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>22.21</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.1838</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>42.63</t>
+          <t>34.77</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD80" t="inlineStr">
         <is>
-          <t>0.3891</t>
+          <t>0.2747</t>
         </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
-          <t>0.1509</t>
+          <t>0.0989</t>
         </is>
       </c>
       <c r="BF80" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="BG80" t="inlineStr"/>
       <c r="BH80" t="inlineStr"/>
       <c r="BI80" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ80" t="inlineStr"/>
@@ -22323,27 +22323,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>686611</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Dylan Crews</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-21T20:10:00Z</t>
+          <t>2026-08-21T23:10:00Z</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -22353,17 +22353,17 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Ryan Gusto</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>687473</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -22372,7 +22372,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -22386,26 +22386,26 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>45.9</v>
+        <v>42.6</v>
       </c>
       <c r="Q81" t="n">
-        <v>17.4</v>
+        <v>48.6</v>
       </c>
       <c r="R81" t="n">
-        <v>27.6</v>
+        <v>21.5</v>
       </c>
       <c r="S81" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T81" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U81" t="n">
-        <v>28.2</v>
+        <v>4.5</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
@@ -22461,12 +22461,12 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
@@ -22476,12 +22476,12 @@
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 0 HR</t>
+          <t>Last 7 games: 3/20, 0 HR</t>
         </is>
       </c>
       <c r="AL81" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.6% barrel, 11.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.9% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
@@ -22491,104 +22491,104 @@
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
         <is>
-          <t>103.328</t>
+          <t>101.1127</t>
         </is>
       </c>
       <c r="AR81" t="inlineStr">
         <is>
-          <t>0.4653</t>
+          <t>0.4147</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.179</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr">
         <is>
-          <t>0.3346</t>
+          <t>0.3154</t>
         </is>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>73.83</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>37.23</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>36.22</t>
+          <t>33.17</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>0.1838</t>
+          <t>0.1461</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>34.77</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="BD81" t="inlineStr">
         <is>
-          <t>0.2747</t>
+          <t>0.4257</t>
         </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
-          <t>0.0989</t>
+          <t>0.1669</t>
         </is>
       </c>
       <c r="BF81" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="BG81" t="inlineStr"/>
       <c r="BH81" t="inlineStr"/>
       <c r="BI81" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ81" t="inlineStr"/>
@@ -22599,27 +22599,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>702616</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-21T23:15:00Z</t>
+          <t>2026-08-21T23:40:00Z</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -22629,22 +22629,22 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Sean Manaea</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>640455</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L82" t="n">
@@ -22662,26 +22662,26 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>26</v>
+        <v>21.6</v>
       </c>
       <c r="Q82" t="n">
-        <v>35.6</v>
+        <v>46.7</v>
       </c>
       <c r="R82" t="n">
-        <v>32.1</v>
+        <v>27.6</v>
       </c>
       <c r="S82" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T82" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U82" t="n">
-        <v>7.9</v>
+        <v>24.9</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr">
@@ -22720,7 +22720,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD82" t="inlineStr"/>
@@ -22737,12 +22737,12 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -22752,12 +22752,12 @@
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 0 HR</t>
+          <t>Last 7 games: 8/28, 0 HR</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 20.3 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.3% barrel, 15.1 HR allowed</t>
         </is>
       </c>
       <c r="AM82" t="inlineStr">
@@ -22767,104 +22767,104 @@
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>87.61</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>98.1022</t>
+          <t>100.1171</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>0.3781</t>
+          <t>0.361</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>0.1385</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr">
         <is>
-          <t>0.3147</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>0.1323</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>42.04</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.31</t>
         </is>
       </c>
       <c r="BD82" t="inlineStr">
         <is>
-          <t>0.3764</t>
+          <t>0.4199</t>
         </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
-          <t>0.1452</t>
+          <t>0.1736</t>
         </is>
       </c>
       <c r="BF82" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="BG82" t="inlineStr"/>
       <c r="BH82" t="inlineStr"/>
       <c r="BI82" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ82" t="inlineStr"/>
@@ -22875,27 +22875,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>807727</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Charles McAdoo</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-21T23:40:00Z</t>
+          <t>2026-08-21T23:05:00Z</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -22905,26 +22905,26 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Sean Manaea</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>640455</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -22938,26 +22938,26 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>21.6</v>
+        <v>25.1</v>
       </c>
       <c r="Q83" t="n">
-        <v>46.7</v>
+        <v>36.4</v>
       </c>
       <c r="R83" t="n">
-        <v>27.6</v>
+        <v>38.2</v>
       </c>
       <c r="S83" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T83" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U83" t="n">
-        <v>24.9</v>
+        <v>44.5</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr">
@@ -23013,12 +23013,12 @@
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
@@ -23028,12 +23028,12 @@
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 0 HR</t>
+          <t>Contact streak: 10/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL83" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.3% barrel, 15.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.1% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM83" t="inlineStr">
@@ -23043,104 +23043,104 @@
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
         <is>
-          <t>100.1171</t>
+          <t>97.1341</t>
         </is>
       </c>
       <c r="AR83" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>0.396</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.141</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.301</t>
         </is>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.166</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>42.04</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>89.31</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="BD83" t="inlineStr">
         <is>
-          <t>0.4199</t>
+          <t>0.3532</t>
         </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
-          <t>0.1736</t>
+          <t>0.1372</t>
         </is>
       </c>
       <c r="BF83" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BG83" t="inlineStr"/>
       <c r="BH83" t="inlineStr"/>
       <c r="BI83" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ83" t="inlineStr"/>
@@ -23151,27 +23151,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>807727</t>
+          <t>702616</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Charles McAdoo</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-21T23:05:00Z</t>
+          <t>2026-08-21T23:15:00Z</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -23186,12 +23186,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -23214,26 +23214,26 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>25.1</v>
+        <v>26</v>
       </c>
       <c r="Q84" t="n">
-        <v>36.4</v>
+        <v>35.6</v>
       </c>
       <c r="R84" t="n">
-        <v>38.2</v>
+        <v>32.1</v>
       </c>
       <c r="S84" t="n">
         <v>88.7</v>
       </c>
       <c r="T84" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U84" t="n">
-        <v>44.5</v>
+        <v>7</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
@@ -23272,7 +23272,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD84" t="inlineStr"/>
@@ -23289,12 +23289,12 @@
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -23304,12 +23304,12 @@
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Contact streak: 10/24 over last 7 games</t>
+          <t>Last 7 games: 5/30, 0 HR</t>
         </is>
       </c>
       <c r="AL84" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.1% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 20.3 HR allowed</t>
         </is>
       </c>
       <c r="AM84" t="inlineStr">
@@ -23319,104 +23319,104 @@
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>87.61</t>
         </is>
       </c>
       <c r="AQ84" t="inlineStr">
         <is>
-          <t>97.1341</t>
+          <t>98.1022</t>
         </is>
       </c>
       <c r="AR84" t="inlineStr">
         <is>
-          <t>0.396</t>
+          <t>0.3781</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>0.1385</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>0.3147</t>
         </is>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>35.34</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>0.1323</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>37.93</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD84" t="inlineStr">
         <is>
-          <t>0.3532</t>
+          <t>0.3764</t>
         </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
-          <t>0.1372</t>
+          <t>0.1452</t>
         </is>
       </c>
       <c r="BF84" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>27.85</t>
         </is>
       </c>
       <c r="BG84" t="inlineStr"/>
       <c r="BH84" t="inlineStr"/>
       <c r="BI84" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ84" t="inlineStr"/>
@@ -23427,27 +23427,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>667472</t>
+          <t>687093</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dane Myers</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-22T01:40:00Z</t>
+          <t>2026-08-22T00:15:00Z</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -23457,17 +23457,17 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Eduardo Rodriguez</t>
+          <t>MacKenzie Gore</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>593958</t>
+          <t>669022</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -23494,22 +23494,22 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>28.2</v>
+        <v>26.4</v>
       </c>
       <c r="Q85" t="n">
-        <v>41.7</v>
+        <v>46.5</v>
       </c>
       <c r="R85" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="S85" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T85" t="n">
         <v>78</v>
       </c>
       <c r="U85" t="n">
-        <v>57.8</v>
+        <v>14.1</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
@@ -23548,7 +23548,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD85" t="inlineStr"/>
@@ -23570,22 +23570,22 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/28, 0 HR</t>
         </is>
       </c>
       <c r="AL85" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 17.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 18.6 HR allowed</t>
         </is>
       </c>
       <c r="AM85" t="inlineStr">
@@ -23595,104 +23595,104 @@
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>38.01</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AQ85" t="inlineStr">
         <is>
-          <t>99.3262</t>
+          <t>99.2686</t>
         </is>
       </c>
       <c r="AR85" t="inlineStr">
         <is>
-          <t>0.3769</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr">
         <is>
-          <t>0.1379</t>
+          <t>0.131</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr">
         <is>
-          <t>0.3131</t>
+          <t>0.309</t>
         </is>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>71.25</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>26.18</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>25.73</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>0.1064</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>42.63</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>87.99</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="BD85" t="inlineStr">
         <is>
-          <t>0.4391</t>
+          <t>0.3891</t>
         </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
-          <t>0.1755</t>
+          <t>0.1509</t>
         </is>
       </c>
       <c r="BF85" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BG85" t="inlineStr"/>
       <c r="BH85" t="inlineStr"/>
       <c r="BI85" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ85" t="inlineStr"/>
@@ -23703,27 +23703,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>662139</t>
+          <t>667472</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Daulton Varsho</t>
+          <t>Dane Myers</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-22T00:10:00Z</t>
+          <t>2026-08-22T01:40:00Z</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -23733,59 +23733,59 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>J.T. Ginn</t>
+          <t>Eduardo Rodriguez</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>669372</t>
+          <t>593958</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L86" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Watch List</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Projected Lineup, Platoon Edge</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="Q86" t="n">
         <v>41.7</v>
       </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>Longshot</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>Watch List</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>Projected Lineup, Platoon Edge</t>
-        </is>
-      </c>
-      <c r="P86" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>30.9</v>
-      </c>
       <c r="R86" t="n">
-        <v>27.6</v>
+        <v>28.2</v>
       </c>
       <c r="S86" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T86" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>57.8</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
@@ -23841,27 +23841,27 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/22, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL86" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 14.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 17.3 HR allowed</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
@@ -23871,104 +23871,104 @@
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>38.01</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>87.66</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>99.5183</t>
+          <t>99.3262</t>
         </is>
       </c>
       <c r="AR86" t="inlineStr">
         <is>
-          <t>0.396</t>
+          <t>0.3769</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>0.1655</t>
+          <t>0.1379</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr">
         <is>
-          <t>0.3004</t>
+          <t>0.3131</t>
         </is>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>71.25</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>36.81</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>26.18</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>25.73</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>0.1798</t>
+          <t>0.1064</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>87.63</t>
+          <t>87.99</t>
         </is>
       </c>
       <c r="BD86" t="inlineStr">
         <is>
-          <t>0.3691</t>
+          <t>0.4391</t>
         </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
-          <t>0.1351</t>
+          <t>0.1755</t>
         </is>
       </c>
       <c r="BF86" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="BG86" t="inlineStr"/>
       <c r="BH86" t="inlineStr"/>
       <c r="BI86" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ86" t="inlineStr"/>
@@ -23979,27 +23979,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>662139</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Daulton Varsho</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-21T23:15:00Z</t>
+          <t>2026-08-22T00:10:00Z</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -24009,26 +24009,26 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Trevor Rogers</t>
+          <t>J.T. Ginn</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>669432</t>
+          <t>669372</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>41.3</v>
+        <v>41.7</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -24046,22 +24046,22 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>36.2</v>
+        <v>34.7</v>
       </c>
       <c r="Q87" t="n">
-        <v>37.9</v>
+        <v>30.9</v>
       </c>
       <c r="R87" t="n">
-        <v>32.1</v>
+        <v>27.6</v>
       </c>
       <c r="S87" t="n">
-        <v>47.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T87" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U87" t="n">
-        <v>33.7</v>
+        <v>0</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -24122,22 +24122,22 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/9, 1 HR</t>
+          <t>Last 7 games: 2/23, 0 HR</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 10.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 14.9 HR allowed</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
@@ -24147,104 +24147,104 @@
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>88.45</t>
+          <t>87.66</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>100.3908</t>
+          <t>99.5183</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
         <is>
-          <t>0.3894</t>
+          <t>0.396</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>0.1566</t>
+          <t>0.1655</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>0.2886</t>
+          <t>0.3004</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>30.34</t>
+          <t>36.81</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>37.67</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>31.19</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>0.1359</t>
+          <t>0.1798</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>87.63</t>
         </is>
       </c>
       <c r="BD87" t="inlineStr">
         <is>
-          <t>0.3921</t>
+          <t>0.3691</t>
         </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
-          <t>0.1496</t>
+          <t>0.1351</t>
         </is>
       </c>
       <c r="BF87" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>23.01</t>
         </is>
       </c>
       <c r="BG87" t="inlineStr"/>
       <c r="BH87" t="inlineStr"/>
       <c r="BI87" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ87" t="inlineStr"/>
@@ -24255,27 +24255,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>687093</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-22T00:15:00Z</t>
+          <t>2026-08-21T23:15:00Z</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -24285,17 +24285,17 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>MacKenzie Gore</t>
+          <t>Trevor Rogers</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>669022</t>
+          <t>669432</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -24322,22 +24322,22 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>26.4</v>
+        <v>36.2</v>
       </c>
       <c r="Q88" t="n">
-        <v>46.5</v>
+        <v>37.9</v>
       </c>
       <c r="R88" t="n">
-        <v>27.6</v>
+        <v>32.1</v>
       </c>
       <c r="S88" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T88" t="n">
         <v>78</v>
       </c>
       <c r="U88" t="n">
-        <v>6</v>
+        <v>33.7</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
@@ -24376,7 +24376,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr"/>
@@ -24393,27 +24393,27 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Last 7 games: 2/9, 1 HR</t>
         </is>
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 18.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 10.9 HR allowed</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
@@ -24423,104 +24423,104 @@
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.45</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>99.2686</t>
+          <t>100.3908</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.3894</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>0.1566</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>0.2886</t>
         </is>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>30.34</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>37.67</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>31.19</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.1359</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>42.63</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD88" t="inlineStr">
         <is>
-          <t>0.3891</t>
+          <t>0.3921</t>
         </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
-          <t>0.1509</t>
+          <t>0.1496</t>
         </is>
       </c>
       <c r="BF88" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="BG88" t="inlineStr"/>
       <c r="BH88" t="inlineStr"/>
       <c r="BI88" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ88" t="inlineStr"/>
@@ -27638,7 +27638,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
@@ -27648,7 +27648,7 @@
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 2/19, 1 HR</t>
         </is>
       </c>
       <c r="AL100" t="inlineStr">
@@ -28047,27 +28047,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>663647</t>
+          <t>677649</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Ezequiel Duran</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-22T01:40:00Z</t>
+          <t>2026-08-22T00:15:00Z</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -28077,17 +28077,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Eduardo Rodriguez</t>
+          <t>Reid Detmers</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>593958</t>
+          <t>672282</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -28096,7 +28096,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>39.2</v>
+        <v>39.4</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
@@ -28114,22 +28114,22 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>31.6</v>
+        <v>19.6</v>
       </c>
       <c r="Q102" t="n">
-        <v>41.7</v>
+        <v>40.4</v>
       </c>
       <c r="R102" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="S102" t="n">
-        <v>40.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T102" t="n">
         <v>78</v>
       </c>
       <c r="U102" t="n">
-        <v>37.8</v>
+        <v>12</v>
       </c>
       <c r="V102" t="inlineStr">
         <is>
@@ -28143,7 +28143,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr">
@@ -28185,27 +28185,27 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/12, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 17.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 13.7 HR allowed</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
@@ -28215,67 +28215,67 @@
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>90.07</t>
+          <t>87.54</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>99.7622</t>
+          <t>98.7631</t>
         </is>
       </c>
       <c r="AR102" t="inlineStr">
         <is>
-          <t>0.3826</t>
+          <t>0.3489</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>0.1397</t>
+          <t>0.1139</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>0.2827</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>24.52</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>36.01</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>27.08</t>
+          <t>21.58</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>0.0948</t>
+          <t>0.1369</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
@@ -28285,34 +28285,34 @@
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>39.58</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>87.99</t>
+          <t>90.03</t>
         </is>
       </c>
       <c r="BD102" t="inlineStr">
         <is>
-          <t>0.4391</t>
+          <t>0.363</t>
         </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
-          <t>0.1755</t>
+          <t>0.1439</t>
         </is>
       </c>
       <c r="BF102" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>28.69</t>
         </is>
       </c>
       <c r="BG102" t="inlineStr"/>
       <c r="BH102" t="inlineStr"/>
       <c r="BI102" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ102" t="inlineStr"/>
@@ -28323,27 +28323,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>663647</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-21T20:10:00Z</t>
+          <t>2026-08-22T01:40:00Z</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -28353,17 +28353,17 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Eduardo Rodriguez</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>593958</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -28372,7 +28372,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>38.9</v>
+        <v>39.2</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
@@ -28386,26 +28386,26 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>37.6</v>
+        <v>31.6</v>
       </c>
       <c r="Q103" t="n">
-        <v>22</v>
+        <v>41.7</v>
       </c>
       <c r="R103" t="n">
-        <v>27.6</v>
+        <v>28.2</v>
       </c>
       <c r="S103" t="n">
-        <v>88.7</v>
+        <v>40.2</v>
       </c>
       <c r="T103" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U103" t="n">
-        <v>2.7</v>
+        <v>37.8</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -28461,27 +28461,27 @@
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/29, 0 HR</t>
+          <t>Last 7 games: 3/12, 1 HR</t>
         </is>
       </c>
       <c r="AL103" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.8% barrel, 8.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 17.3 HR allowed</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr">
@@ -28491,104 +28491,104 @@
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>43.83</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>90.61</t>
+          <t>90.07</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>100.4496</t>
+          <t>99.7622</t>
         </is>
       </c>
       <c r="AR103" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.3826</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>0.1397</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr">
         <is>
-          <t>0.3406</t>
+          <t>0.296</t>
         </is>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>70.18</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>27.23</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>27.08</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>0.1694</t>
+          <t>0.0948</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>34.77</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>87.99</t>
         </is>
       </c>
       <c r="BD103" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>0.4391</t>
         </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
-          <t>0.1094</t>
+          <t>0.1755</t>
         </is>
       </c>
       <c r="BF103" t="inlineStr">
         <is>
-          <t>25.69</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="BG103" t="inlineStr"/>
       <c r="BH103" t="inlineStr"/>
       <c r="BI103" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ103" t="inlineStr"/>
@@ -28599,27 +28599,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>677649</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ezequiel Duran</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-22T00:15:00Z</t>
+          <t>2026-08-21T20:10:00Z</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -28629,17 +28629,17 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Reid Detmers</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>672282</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -28662,26 +28662,26 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>19.6</v>
+        <v>37.6</v>
       </c>
       <c r="Q104" t="n">
-        <v>40.4</v>
+        <v>22</v>
       </c>
       <c r="R104" t="n">
         <v>27.6</v>
       </c>
       <c r="S104" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T104" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U104" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -28752,12 +28752,12 @@
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/23, 0 HR</t>
+          <t>Last 7 games: 4/29, 0 HR</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 13.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.8% barrel, 8.9 HR allowed</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr">
@@ -28767,104 +28767,104 @@
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>43.83</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>87.54</t>
+          <t>90.61</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>98.7631</t>
+          <t>100.4496</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>0.3489</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>0.1139</t>
+          <t>0.174</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>0.2827</t>
+          <t>0.3406</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>70.18</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>24.52</t>
+          <t>12.92</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>36.01</t>
+          <t>27.23</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>0.1369</t>
+          <t>0.1694</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>34.77</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>90.03</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD104" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>0.327</t>
         </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
-          <t>0.1439</t>
+          <t>0.1094</t>
         </is>
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>25.69</t>
         </is>
       </c>
       <c r="BG104" t="inlineStr"/>
       <c r="BH104" t="inlineStr"/>
       <c r="BI104" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ104" t="inlineStr"/>
@@ -29200,7 +29200,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>50</v>
       </c>
       <c r="U106" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
@@ -29304,7 +29304,7 @@
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL106" t="inlineStr">
@@ -29476,7 +29476,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>75</v>
       </c>
       <c r="U107" t="n">
-        <v>34.2</v>
+        <v>32</v>
       </c>
       <c r="V107" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
@@ -29580,7 +29580,7 @@
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Contact streak: 8/23 over last 7 games</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL107" t="inlineStr">
@@ -31132,7 +31132,7 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>50</v>
       </c>
       <c r="U113" t="n">
-        <v>52.5</v>
+        <v>50.3</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
@@ -31236,7 +31236,7 @@
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>Contact streak: 8/23 over last 7 games</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL113" t="inlineStr">
@@ -31635,27 +31635,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>664774</t>
+          <t>691458</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>LaMonte Wade</t>
+          <t>Blaze Jordan</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-22T00:10:00Z</t>
+          <t>2026-08-21T22:40:00Z</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -31665,26 +31665,26 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>J.T. Ginn</t>
+          <t>Jesús Luzardo</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>669372</t>
+          <t>666200</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
@@ -31698,26 +31698,26 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P115" t="n">
-        <v>14.2</v>
+        <v>33.6</v>
       </c>
       <c r="Q115" t="n">
-        <v>30.9</v>
+        <v>21.4</v>
       </c>
       <c r="R115" t="n">
-        <v>27.6</v>
+        <v>34.3</v>
       </c>
       <c r="S115" t="n">
-        <v>88.7</v>
+        <v>47.9</v>
       </c>
       <c r="T115" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U115" t="n">
-        <v>22.9</v>
+        <v>33.7</v>
       </c>
       <c r="V115" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y115" t="inlineStr">
@@ -31756,7 +31756,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD115" t="inlineStr"/>
@@ -31773,27 +31773,27 @@
       </c>
       <c r="AH115" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/11, 0 HR</t>
+          <t>Last 7 games: 6/27, 1 HR</t>
         </is>
       </c>
       <c r="AL115" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 14.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.1% barrel, 13.2 HR allowed</t>
         </is>
       </c>
       <c r="AM115" t="inlineStr">
@@ -31803,57 +31803,57 @@
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>87.53</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>98.2628</t>
+          <t>99.8674</t>
         </is>
       </c>
       <c r="AR115" t="inlineStr">
         <is>
-          <t>0.3021</t>
+          <t>0.407</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>0.0971</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>0.309</t>
         </is>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>70.91</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>37.77</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -31863,44 +31863,44 @@
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>0.1094</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>87.63</t>
+          <t>87.59</t>
         </is>
       </c>
       <c r="BD115" t="inlineStr">
         <is>
-          <t>0.3691</t>
+          <t>0.3193</t>
         </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
-          <t>0.1351</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="BF115" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="BG115" t="inlineStr"/>
       <c r="BH115" t="inlineStr"/>
       <c r="BI115" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ115" t="inlineStr"/>
@@ -31911,27 +31911,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>691458</t>
+          <t>664774</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Blaze Jordan</t>
+          <t>LaMonte Wade</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-21T22:40:00Z</t>
+          <t>2026-08-22T00:10:00Z</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -31941,26 +31941,26 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Jesús Luzardo</t>
+          <t>J.T. Ginn</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>666200</t>
+          <t>669372</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
@@ -31974,26 +31974,26 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P116" t="n">
-        <v>33.6</v>
+        <v>14.2</v>
       </c>
       <c r="Q116" t="n">
-        <v>21.4</v>
+        <v>30.9</v>
       </c>
       <c r="R116" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S116" t="n">
-        <v>47.9</v>
+        <v>88.7</v>
       </c>
       <c r="T116" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U116" t="n">
-        <v>33.7</v>
+        <v>16.6</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
@@ -32032,7 +32032,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr"/>
@@ -32049,27 +32049,27 @@
       </c>
       <c r="AH116" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 1 HR</t>
+          <t>Last 7 games: 3/13, 0 HR</t>
         </is>
       </c>
       <c r="AL116" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.1% barrel, 13.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 14.9 HR allowed</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
@@ -32079,57 +32079,57 @@
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>33.97</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.53</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>99.8674</t>
+          <t>98.2628</t>
         </is>
       </c>
       <c r="AR116" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>0.3021</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.0971</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>0.288</t>
         </is>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>70.91</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>37.77</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>24.74</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -32139,44 +32139,44 @@
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.1094</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>87.59</t>
+          <t>87.63</t>
         </is>
       </c>
       <c r="BD116" t="inlineStr">
         <is>
-          <t>0.3193</t>
+          <t>0.3691</t>
         </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.1351</t>
         </is>
       </c>
       <c r="BF116" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>23.01</t>
         </is>
       </c>
       <c r="BG116" t="inlineStr"/>
       <c r="BH116" t="inlineStr"/>
       <c r="BI116" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ116" t="inlineStr"/>
@@ -33158,7 +33158,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
@@ -33168,7 +33168,7 @@
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 2/20, 0 HR</t>
         </is>
       </c>
       <c r="AL120" t="inlineStr">
@@ -38617,7 +38617,7 @@
         <v>50</v>
       </c>
       <c r="U140" t="n">
-        <v>14.6</v>
+        <v>13.3</v>
       </c>
       <c r="V140" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ140" t="inlineStr">
@@ -38688,7 +38688,7 @@
       </c>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL140" t="inlineStr">
@@ -40516,7 +40516,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>75</v>
       </c>
       <c r="U147" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="V147" t="inlineStr">
         <is>
@@ -40610,7 +40610,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
@@ -40620,7 +40620,7 @@
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
@@ -41150,7 +41150,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ149" t="inlineStr">
@@ -41160,7 +41160,7 @@
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/11, 0 HR</t>
+          <t>Last 7 games: 1/12, 0 HR</t>
         </is>
       </c>
       <c r="AL149" t="inlineStr">
@@ -41584,7 +41584,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>75</v>
       </c>
       <c r="U151" t="n">
-        <v>14.1</v>
+        <v>17.3</v>
       </c>
       <c r="V151" t="inlineStr">
         <is>
@@ -41673,12 +41673,12 @@
       </c>
       <c r="AH151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ151" t="inlineStr">
@@ -41688,7 +41688,7 @@
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/14, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL151" t="inlineStr">
@@ -42501,12 +42501,12 @@
       </c>
       <c r="AH154" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ154" t="inlineStr">
@@ -42516,7 +42516,7 @@
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>Contact streak: 7/15 over last 7 games</t>
+          <t>Contact streak: 8/18 over last 7 games</t>
         </is>
       </c>
       <c r="AL154" t="inlineStr">
@@ -43743,24 +43743,24 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>687231</t>
+          <t>543877</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Darell Hernaiz</t>
+          <t>Christian Vazquez</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
           <t>ATH</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F159" t="inlineStr">
         <is>
           <t>2026-08-22T00:10:00Z</t>
@@ -43778,12 +43778,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Hayden Wesneski</t>
+          <t>J.T. Ginn</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>669713</t>
+          <t>669372</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -43792,7 +43792,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="M159" t="inlineStr">
         <is>
@@ -43810,10 +43810,10 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q159" t="n">
-        <v>42.1</v>
+        <v>30.9</v>
       </c>
       <c r="R159" t="n">
         <v>27.6</v>
@@ -43825,7 +43825,7 @@
         <v>50</v>
       </c>
       <c r="U159" t="n">
-        <v>0</v>
+        <v>56.2</v>
       </c>
       <c r="V159" t="inlineStr">
         <is>
@@ -43881,27 +43881,27 @@
       </c>
       <c r="AH159" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK159" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL159" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 3.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 14.9 HR allowed</t>
         </is>
       </c>
       <c r="AM159" t="inlineStr">
@@ -43911,97 +43911,97 @@
       </c>
       <c r="AN159" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>24.88</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>84.79</t>
+          <t>85.97</t>
         </is>
       </c>
       <c r="AQ159" t="inlineStr">
         <is>
-          <t>96.112</t>
+          <t>95.6723</t>
         </is>
       </c>
       <c r="AR159" t="inlineStr">
         <is>
-          <t>0.2971</t>
+          <t>0.2881</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr">
         <is>
-          <t>0.0677</t>
+          <t>0.0851</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr">
         <is>
-          <t>0.2756</t>
+          <t>0.2514</t>
         </is>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>34.28</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>0.0561</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>89.56</t>
+          <t>87.63</t>
         </is>
       </c>
       <c r="BD159" t="inlineStr">
         <is>
-          <t>0.4227</t>
+          <t>0.3691</t>
         </is>
       </c>
       <c r="BE159" t="inlineStr">
         <is>
-          <t>0.1627</t>
+          <t>0.1351</t>
         </is>
       </c>
       <c r="BF159" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>23.01</t>
         </is>
       </c>
       <c r="BG159" t="inlineStr"/>
@@ -44019,24 +44019,24 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>543877</t>
+          <t>687231</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Christian Vazquez</t>
+          <t>Darell Hernaiz</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
+          <t>ATH</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>ATH</t>
-        </is>
-      </c>
       <c r="F160" t="inlineStr">
         <is>
           <t>2026-08-22T00:10:00Z</t>
@@ -44054,12 +44054,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>J.T. Ginn</t>
+          <t>Hayden Wesneski</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>669372</t>
+          <t>669713</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -44068,7 +44068,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="M160" t="inlineStr">
         <is>
@@ -44086,10 +44086,10 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q160" t="n">
-        <v>30.9</v>
+        <v>42.1</v>
       </c>
       <c r="R160" t="n">
         <v>27.6</v>
@@ -44101,7 +44101,7 @@
         <v>50</v>
       </c>
       <c r="U160" t="n">
-        <v>50.8</v>
+        <v>0</v>
       </c>
       <c r="V160" t="inlineStr">
         <is>
@@ -44157,27 +44157,27 @@
       </c>
       <c r="AH160" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL160" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 14.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 3.5 HR allowed</t>
         </is>
       </c>
       <c r="AM160" t="inlineStr">
@@ -44187,97 +44187,97 @@
       </c>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>24.88</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>85.97</t>
+          <t>84.79</t>
         </is>
       </c>
       <c r="AQ160" t="inlineStr">
         <is>
-          <t>95.6723</t>
+          <t>96.112</t>
         </is>
       </c>
       <c r="AR160" t="inlineStr">
         <is>
-          <t>0.2881</t>
+          <t>0.2971</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr">
         <is>
-          <t>0.0851</t>
+          <t>0.0677</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr">
         <is>
-          <t>0.2514</t>
+          <t>0.2756</t>
         </is>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0561</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>42.03</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>87.63</t>
+          <t>89.56</t>
         </is>
       </c>
       <c r="BD160" t="inlineStr">
         <is>
-          <t>0.3691</t>
+          <t>0.4227</t>
         </is>
       </c>
       <c r="BE160" t="inlineStr">
         <is>
-          <t>0.1351</t>
+          <t>0.1627</t>
         </is>
       </c>
       <c r="BF160" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="BG160" t="inlineStr"/>
@@ -44295,27 +44295,27 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>669397</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Nick Allen</t>
+          <t>Mauricio Dubon</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-22T00:10:00Z</t>
+          <t>2026-08-21T20:10:00Z</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -44325,17 +44325,17 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>J.T. Ginn</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>669372</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -44344,7 +44344,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="M161" t="inlineStr">
         <is>
@@ -44362,22 +44362,22 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>2.5</v>
+        <v>10.6</v>
       </c>
       <c r="Q161" t="n">
-        <v>30.9</v>
+        <v>17.4</v>
       </c>
       <c r="R161" t="n">
         <v>27.6</v>
       </c>
       <c r="S161" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T161" t="n">
         <v>50</v>
       </c>
       <c r="U161" t="n">
-        <v>37.8</v>
+        <v>14.6</v>
       </c>
       <c r="V161" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y161" t="inlineStr">
@@ -44433,27 +44433,27 @@
       </c>
       <c r="AH161" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/12, 1 HR</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL161" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 14.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.6% barrel, 11.5 HR allowed</t>
         </is>
       </c>
       <c r="AM161" t="inlineStr">
@@ -44463,104 +44463,104 @@
       </c>
       <c r="AN161" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>24.54</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>85.08</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AQ161" t="inlineStr">
         <is>
-          <t>95.6512</t>
+          <t>96.3025</t>
         </is>
       </c>
       <c r="AR161" t="inlineStr">
         <is>
-          <t>0.2614</t>
+          <t>0.3639</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr">
         <is>
-          <t>0.0523</t>
+          <t>0.1029</t>
         </is>
       </c>
       <c r="AT161" t="inlineStr">
         <is>
-          <t>0.2373</t>
+          <t>0.2969</t>
         </is>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>67.51</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>32.45</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>0.0699</t>
+          <t>0.1231</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>34.77</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>87.63</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD161" t="inlineStr">
         <is>
-          <t>0.3691</t>
+          <t>0.2747</t>
         </is>
       </c>
       <c r="BE161" t="inlineStr">
         <is>
-          <t>0.1351</t>
+          <t>0.0989</t>
         </is>
       </c>
       <c r="BF161" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="BG161" t="inlineStr"/>
       <c r="BH161" t="inlineStr"/>
       <c r="BI161" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ161" t="inlineStr"/>
@@ -44571,27 +44571,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>669397</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Nick Allen</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-08-21T20:10:00Z</t>
+          <t>2026-08-22T00:10:00Z</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -44601,17 +44601,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>J.T. Ginn</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>669372</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -44620,7 +44620,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>25.4</v>
+        <v>25.2</v>
       </c>
       <c r="M162" t="inlineStr">
         <is>
@@ -44638,22 +44638,22 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>10.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q162" t="n">
-        <v>17.4</v>
+        <v>30.9</v>
       </c>
       <c r="R162" t="n">
         <v>27.6</v>
       </c>
       <c r="S162" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T162" t="n">
         <v>50</v>
       </c>
       <c r="U162" t="n">
-        <v>14.6</v>
+        <v>32.5</v>
       </c>
       <c r="V162" t="inlineStr">
         <is>
@@ -44667,7 +44667,7 @@
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y162" t="inlineStr">
@@ -44709,27 +44709,27 @@
       </c>
       <c r="AH162" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 3/14, 1 HR</t>
         </is>
       </c>
       <c r="AL162" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.6% barrel, 11.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 14.9 HR allowed</t>
         </is>
       </c>
       <c r="AM162" t="inlineStr">
@@ -44739,104 +44739,104 @@
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>28.82</t>
+          <t>24.54</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>86.11</t>
+          <t>85.08</t>
         </is>
       </c>
       <c r="AQ162" t="inlineStr">
         <is>
-          <t>96.3025</t>
+          <t>95.6512</t>
         </is>
       </c>
       <c r="AR162" t="inlineStr">
         <is>
-          <t>0.3639</t>
+          <t>0.2614</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
         <is>
-          <t>0.1029</t>
+          <t>0.0523</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr">
         <is>
-          <t>0.2969</t>
+          <t>0.2373</t>
         </is>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>67.51</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>0.1231</t>
+          <t>0.0699</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>34.77</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.63</t>
         </is>
       </c>
       <c r="BD162" t="inlineStr">
         <is>
-          <t>0.2747</t>
+          <t>0.3691</t>
         </is>
       </c>
       <c r="BE162" t="inlineStr">
         <is>
-          <t>0.0989</t>
+          <t>0.1351</t>
         </is>
       </c>
       <c r="BF162" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>23.01</t>
         </is>
       </c>
       <c r="BG162" t="inlineStr"/>
       <c r="BH162" t="inlineStr"/>
       <c r="BI162" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ162" t="inlineStr"/>
@@ -46083,7 +46083,7 @@
         <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>51.3</v>
+        <v>49.9</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -46144,7 +46144,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -46696,7 +46696,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -47451,7 +47451,7 @@
         <v>60</v>
       </c>
       <c r="U9" t="n">
-        <v>40.9</v>
+        <v>40.1</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -47512,7 +47512,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -47670,7 +47670,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>56.6</v>
+        <v>56.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -47703,7 +47703,7 @@
         <v>78</v>
       </c>
       <c r="U10" t="n">
-        <v>16.6</v>
+        <v>15.3</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -47764,7 +47764,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -47774,7 +47774,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -48311,12 +48311,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -50118,7 +50118,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>52.8</v>
+        <v>52.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>68.7</v>
+        <v>63.7</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -50394,7 +50394,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>50</v>
       </c>
       <c r="U20" t="n">
-        <v>54.7</v>
+        <v>53.3</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -50621,24 +50621,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>669394</t>
+          <t>687263</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jake Burger</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>2026-08-22T00:15:00Z</t>
@@ -50651,17 +50651,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Reid Detmers</t>
+          <t>MacKenzie Gore</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>672282</t>
+          <t>669022</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -50688,22 +50688,22 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>48.5</v>
+        <v>46.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>40.4</v>
+        <v>46.5</v>
       </c>
       <c r="R21" t="n">
         <v>27.6</v>
       </c>
       <c r="S21" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T21" t="n">
         <v>78</v>
       </c>
       <c r="U21" t="n">
-        <v>56.2</v>
+        <v>46.5</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -50717,7 +50717,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -50759,27 +50759,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 13.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 18.6 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -50789,97 +50789,97 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>89.74</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>102.6757</t>
+          <t>100.102</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4227</t>
+          <t>0.4166</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.1872</t>
+          <t>0.2027</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3086</t>
+          <t>0.3097</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>75.37</t>
+          <t>71.26</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>58.14</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>41.88</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>34.96</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1844</t>
+          <t>0.1946</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>42.63</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>90.03</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>0.3891</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1439</t>
+          <t>0.1509</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-08-20_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-20_remaining.xlsx
@@ -5355,27 +5355,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>665953</t>
+          <t>687263</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Andres Chaparro</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-21T23:10:00Z</t>
+          <t>2026-08-22T00:15:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -5385,26 +5385,26 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Ryan Gusto</t>
+          <t>MacKenzie Gore</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>687473</t>
+          <t>669022</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>52.6</v>
+        <v>52.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5418,26 +5418,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>51.9</v>
+        <v>46.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>48.6</v>
+        <v>46.5</v>
       </c>
       <c r="R19" t="n">
-        <v>21.5</v>
+        <v>27.6</v>
       </c>
       <c r="S19" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U19" t="n">
-        <v>63.7</v>
+        <v>50.3</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -5493,27 +5493,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.9% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 18.6 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5523,104 +5523,104 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>88.45</t>
+          <t>89.74</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>101.3034</t>
+          <t>100.102</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4503</t>
+          <t>0.4166</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.2219</t>
+          <t>0.2027</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3392</t>
+          <t>0.3097</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>74.14</t>
+          <t>71.26</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>43.28</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>48.59</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>28.26</t>
+          <t>34.96</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.2279</t>
+          <t>0.1946</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>42.63</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.4257</t>
+          <t>0.3891</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1669</t>
+          <t>0.1509</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr"/>
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr"/>
@@ -5631,27 +5631,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>687952</t>
+          <t>665953</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Christian Encarnacion-Strand</t>
+          <t>Andres Chaparro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-21T23:15:00Z</t>
+          <t>2026-08-21T23:10:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -5661,17 +5661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Ryan Gusto</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>687473</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -5694,26 +5694,26 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>62.5</v>
+        <v>51.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>35.6</v>
+        <v>48.6</v>
       </c>
       <c r="R20" t="n">
-        <v>32.1</v>
+        <v>21.5</v>
       </c>
       <c r="S20" t="n">
-        <v>81.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T20" t="n">
         <v>50</v>
       </c>
       <c r="U20" t="n">
-        <v>53.3</v>
+        <v>63.7</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 20.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.9% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -5799,104 +5799,104 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>42.74</t>
+          <t>45.92</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>88.45</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>101.9926</t>
+          <t>101.3034</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.5177</t>
+          <t>0.4503</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.2738</t>
+          <t>0.2219</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3357</t>
+          <t>0.3392</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>73.67</t>
+          <t>74.14</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>43.28</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>48.59</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>29.79</t>
+          <t>28.26</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2279</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.3764</t>
+          <t>0.4257</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.1452</t>
+          <t>0.1669</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr"/>
       <c r="BH20" t="inlineStr"/>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -5907,27 +5907,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>687263</t>
+          <t>687952</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Christian Encarnacion-Strand</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-22T00:15:00Z</t>
+          <t>2026-08-21T23:15:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -5937,22 +5937,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MacKenzie Gore</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>669022</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -5970,26 +5970,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>46.3</v>
+        <v>62.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>46.5</v>
+        <v>35.6</v>
       </c>
       <c r="R21" t="n">
-        <v>27.6</v>
+        <v>32.1</v>
       </c>
       <c r="S21" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>46.5</v>
+        <v>53.3</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
@@ -6055,17 +6055,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 18.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 20.3 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -6075,104 +6075,104 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>42.74</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>89.74</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>100.102</t>
+          <t>101.9926</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4166</t>
+          <t>0.5177</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.2027</t>
+          <t>0.2738</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.3357</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>71.26</t>
+          <t>73.67</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>34.96</t>
+          <t>29.79</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1946</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>42.63</t>
+          <t>37.93</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.3891</t>
+          <t>0.3764</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1509</t>
+          <t>0.1452</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.85</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr"/>
       <c r="BH21" t="inlineStr"/>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
@@ -21648,7 +21648,7 @@
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/21, 0 HR</t>
+          <t>Last 7 games: 1/22, 0 HR</t>
         </is>
       </c>
       <c r="AL78" t="inlineStr">
@@ -21820,7 +21820,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>50</v>
       </c>
       <c r="U79" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 4/27, 0 HR</t>
         </is>
       </c>
       <c r="AL79" t="inlineStr">
@@ -23427,27 +23427,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>687093</t>
+          <t>667472</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>Dane Myers</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-22T00:15:00Z</t>
+          <t>2026-08-22T01:40:00Z</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -23457,17 +23457,17 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>MacKenzie Gore</t>
+          <t>Eduardo Rodriguez</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>669022</t>
+          <t>593958</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -23494,22 +23494,22 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>26.4</v>
+        <v>28.2</v>
       </c>
       <c r="Q85" t="n">
-        <v>46.5</v>
+        <v>41.7</v>
       </c>
       <c r="R85" t="n">
-        <v>27.6</v>
+        <v>28.2</v>
       </c>
       <c r="S85" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T85" t="n">
         <v>78</v>
       </c>
       <c r="U85" t="n">
-        <v>14.1</v>
+        <v>57.8</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
@@ -23548,7 +23548,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD85" t="inlineStr"/>
@@ -23570,22 +23570,22 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL85" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 18.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 17.3 HR allowed</t>
         </is>
       </c>
       <c r="AM85" t="inlineStr">
@@ -23595,104 +23595,104 @@
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.01</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="AQ85" t="inlineStr">
         <is>
-          <t>99.2686</t>
+          <t>99.3262</t>
         </is>
       </c>
       <c r="AR85" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.3769</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>0.1379</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>0.3131</t>
         </is>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.25</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>26.18</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.73</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.1064</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>42.63</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>87.99</t>
         </is>
       </c>
       <c r="BD85" t="inlineStr">
         <is>
-          <t>0.3891</t>
+          <t>0.4391</t>
         </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
-          <t>0.1509</t>
+          <t>0.1755</t>
         </is>
       </c>
       <c r="BF85" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="BG85" t="inlineStr"/>
       <c r="BH85" t="inlineStr"/>
       <c r="BI85" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ85" t="inlineStr"/>
@@ -23703,27 +23703,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>667472</t>
+          <t>662139</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dane Myers</t>
+          <t>Daulton Varsho</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-22T01:40:00Z</t>
+          <t>2026-08-22T00:10:00Z</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -23733,26 +23733,26 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Eduardo Rodriguez</t>
+          <t>J.T. Ginn</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>593958</t>
+          <t>669372</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -23770,22 +23770,22 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>28.2</v>
+        <v>34.7</v>
       </c>
       <c r="Q86" t="n">
-        <v>41.7</v>
+        <v>30.9</v>
       </c>
       <c r="R86" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="S86" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T86" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U86" t="n">
-        <v>57.8</v>
+        <v>0.8</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
@@ -23841,27 +23841,27 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL86" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 17.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 14.9 HR allowed</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
@@ -23871,104 +23871,104 @@
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>38.01</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>87.66</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>99.3262</t>
+          <t>99.5183</t>
         </is>
       </c>
       <c r="AR86" t="inlineStr">
         <is>
-          <t>0.3769</t>
+          <t>0.396</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>0.1379</t>
+          <t>0.1655</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr">
         <is>
-          <t>0.3131</t>
+          <t>0.3004</t>
         </is>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>71.25</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>36.81</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>26.18</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>25.73</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>0.1064</t>
+          <t>0.1798</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>87.99</t>
+          <t>87.63</t>
         </is>
       </c>
       <c r="BD86" t="inlineStr">
         <is>
-          <t>0.4391</t>
+          <t>0.3691</t>
         </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
-          <t>0.1755</t>
+          <t>0.1351</t>
         </is>
       </c>
       <c r="BF86" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>23.01</t>
         </is>
       </c>
       <c r="BG86" t="inlineStr"/>
       <c r="BH86" t="inlineStr"/>
       <c r="BI86" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ86" t="inlineStr"/>
@@ -23979,27 +23979,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>662139</t>
+          <t>687093</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Daulton Varsho</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-22T00:10:00Z</t>
+          <t>2026-08-22T00:15:00Z</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -24009,22 +24009,22 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>J.T. Ginn</t>
+          <t>MacKenzie Gore</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>669372</t>
+          <t>669022</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L87" t="n">
@@ -24046,22 +24046,22 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>34.7</v>
+        <v>26.4</v>
       </c>
       <c r="Q87" t="n">
-        <v>30.9</v>
+        <v>46.5</v>
       </c>
       <c r="R87" t="n">
         <v>27.6</v>
       </c>
       <c r="S87" t="n">
-        <v>81.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T87" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -24100,7 +24100,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr"/>
@@ -24117,12 +24117,12 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -24132,12 +24132,12 @@
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/23, 0 HR</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 14.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 18.6 HR allowed</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
@@ -24147,104 +24147,104 @@
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>87.66</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>99.5183</t>
+          <t>99.2686</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
         <is>
-          <t>0.396</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>0.1655</t>
+          <t>0.131</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>0.3004</t>
+          <t>0.309</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>36.81</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>0.1798</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>42.63</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>87.63</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="BD87" t="inlineStr">
         <is>
-          <t>0.3691</t>
+          <t>0.3891</t>
         </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
-          <t>0.1351</t>
+          <t>0.1509</t>
         </is>
       </c>
       <c r="BF87" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BG87" t="inlineStr"/>
       <c r="BH87" t="inlineStr"/>
       <c r="BI87" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ87" t="inlineStr"/>
@@ -31132,7 +31132,7 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>37.5</v>
+        <v>37.7</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>50</v>
       </c>
       <c r="U113" t="n">
-        <v>50.3</v>
+        <v>54.3</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -31221,12 +31221,12 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
@@ -31236,7 +31236,7 @@
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL113" t="inlineStr">
@@ -43743,24 +43743,24 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>543877</t>
+          <t>687231</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Christian Vazquez</t>
+          <t>Darell Hernaiz</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
+          <t>ATH</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>ATH</t>
-        </is>
-      </c>
       <c r="F159" t="inlineStr">
         <is>
           <t>2026-08-22T00:10:00Z</t>
@@ -43778,12 +43778,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>J.T. Ginn</t>
+          <t>Hayden Wesneski</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>669372</t>
+          <t>669713</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -43792,7 +43792,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="M159" t="inlineStr">
         <is>
@@ -43810,10 +43810,10 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q159" t="n">
-        <v>30.9</v>
+        <v>42.1</v>
       </c>
       <c r="R159" t="n">
         <v>27.6</v>
@@ -43825,7 +43825,7 @@
         <v>50</v>
       </c>
       <c r="U159" t="n">
-        <v>56.2</v>
+        <v>0</v>
       </c>
       <c r="V159" t="inlineStr">
         <is>
@@ -43881,27 +43881,27 @@
       </c>
       <c r="AH159" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI159" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL159" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 14.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 3.5 HR allowed</t>
         </is>
       </c>
       <c r="AM159" t="inlineStr">
@@ -43911,97 +43911,97 @@
       </c>
       <c r="AN159" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>24.88</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>85.97</t>
+          <t>84.79</t>
         </is>
       </c>
       <c r="AQ159" t="inlineStr">
         <is>
-          <t>95.6723</t>
+          <t>96.112</t>
         </is>
       </c>
       <c r="AR159" t="inlineStr">
         <is>
-          <t>0.2881</t>
+          <t>0.2971</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr">
         <is>
-          <t>0.0851</t>
+          <t>0.0677</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr">
         <is>
-          <t>0.2514</t>
+          <t>0.2756</t>
         </is>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0561</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>42.03</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>87.63</t>
+          <t>89.56</t>
         </is>
       </c>
       <c r="BD159" t="inlineStr">
         <is>
-          <t>0.3691</t>
+          <t>0.4227</t>
         </is>
       </c>
       <c r="BE159" t="inlineStr">
         <is>
-          <t>0.1351</t>
+          <t>0.1627</t>
         </is>
       </c>
       <c r="BF159" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="BG159" t="inlineStr"/>
@@ -44019,24 +44019,24 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>687231</t>
+          <t>543877</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Darell Hernaiz</t>
+          <t>Christian Vazquez</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
           <t>ATH</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F160" t="inlineStr">
         <is>
           <t>2026-08-22T00:10:00Z</t>
@@ -44054,12 +44054,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Hayden Wesneski</t>
+          <t>J.T. Ginn</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>669713</t>
+          <t>669372</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -44086,10 +44086,10 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q160" t="n">
-        <v>42.1</v>
+        <v>30.9</v>
       </c>
       <c r="R160" t="n">
         <v>27.6</v>
@@ -44101,7 +44101,7 @@
         <v>50</v>
       </c>
       <c r="U160" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="V160" t="inlineStr">
         <is>
@@ -44157,27 +44157,27 @@
       </c>
       <c r="AH160" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI160" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK160" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL160" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 3.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 14.9 HR allowed</t>
         </is>
       </c>
       <c r="AM160" t="inlineStr">
@@ -44187,97 +44187,97 @@
       </c>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>24.88</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>84.79</t>
+          <t>85.97</t>
         </is>
       </c>
       <c r="AQ160" t="inlineStr">
         <is>
-          <t>96.112</t>
+          <t>95.6723</t>
         </is>
       </c>
       <c r="AR160" t="inlineStr">
         <is>
-          <t>0.2971</t>
+          <t>0.2881</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr">
         <is>
-          <t>0.0677</t>
+          <t>0.0851</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr">
         <is>
-          <t>0.2756</t>
+          <t>0.2514</t>
         </is>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>34.28</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>0.0561</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>89.56</t>
+          <t>87.63</t>
         </is>
       </c>
       <c r="BD160" t="inlineStr">
         <is>
-          <t>0.4227</t>
+          <t>0.3691</t>
         </is>
       </c>
       <c r="BE160" t="inlineStr">
         <is>
-          <t>0.1627</t>
+          <t>0.1351</t>
         </is>
       </c>
       <c r="BF160" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>23.01</t>
         </is>
       </c>
       <c r="BG160" t="inlineStr"/>
@@ -44295,27 +44295,27 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>669397</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Nick Allen</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-21T20:10:00Z</t>
+          <t>2026-08-22T00:10:00Z</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -44325,17 +44325,17 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>J.T. Ginn</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>669372</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -44344,7 +44344,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="M161" t="inlineStr">
         <is>
@@ -44362,22 +44362,22 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>10.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q161" t="n">
-        <v>17.4</v>
+        <v>30.9</v>
       </c>
       <c r="R161" t="n">
         <v>27.6</v>
       </c>
       <c r="S161" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T161" t="n">
         <v>50</v>
       </c>
       <c r="U161" t="n">
-        <v>14.6</v>
+        <v>40.3</v>
       </c>
       <c r="V161" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y161" t="inlineStr">
@@ -44433,27 +44433,27 @@
       </c>
       <c r="AH161" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 4/15, 1 HR</t>
         </is>
       </c>
       <c r="AL161" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.6% barrel, 11.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 14.9 HR allowed</t>
         </is>
       </c>
       <c r="AM161" t="inlineStr">
@@ -44463,104 +44463,104 @@
       </c>
       <c r="AN161" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>28.82</t>
+          <t>24.54</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>86.11</t>
+          <t>85.08</t>
         </is>
       </c>
       <c r="AQ161" t="inlineStr">
         <is>
-          <t>96.3025</t>
+          <t>95.6512</t>
         </is>
       </c>
       <c r="AR161" t="inlineStr">
         <is>
-          <t>0.3639</t>
+          <t>0.2614</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr">
         <is>
-          <t>0.1029</t>
+          <t>0.0523</t>
         </is>
       </c>
       <c r="AT161" t="inlineStr">
         <is>
-          <t>0.2969</t>
+          <t>0.2373</t>
         </is>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>67.51</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>0.1231</t>
+          <t>0.0699</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>34.77</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.63</t>
         </is>
       </c>
       <c r="BD161" t="inlineStr">
         <is>
-          <t>0.2747</t>
+          <t>0.3691</t>
         </is>
       </c>
       <c r="BE161" t="inlineStr">
         <is>
-          <t>0.0989</t>
+          <t>0.1351</t>
         </is>
       </c>
       <c r="BF161" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>23.01</t>
         </is>
       </c>
       <c r="BG161" t="inlineStr"/>
       <c r="BH161" t="inlineStr"/>
       <c r="BI161" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ161" t="inlineStr"/>
@@ -44571,27 +44571,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>669397</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Nick Allen</t>
+          <t>Mauricio Dubon</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-08-22T00:10:00Z</t>
+          <t>2026-08-21T20:10:00Z</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -44601,17 +44601,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>J.T. Ginn</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>669372</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -44620,7 +44620,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="M162" t="inlineStr">
         <is>
@@ -44638,22 +44638,22 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>2.5</v>
+        <v>10.6</v>
       </c>
       <c r="Q162" t="n">
-        <v>30.9</v>
+        <v>17.4</v>
       </c>
       <c r="R162" t="n">
         <v>27.6</v>
       </c>
       <c r="S162" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T162" t="n">
         <v>50</v>
       </c>
       <c r="U162" t="n">
-        <v>32.5</v>
+        <v>14.6</v>
       </c>
       <c r="V162" t="inlineStr">
         <is>
@@ -44667,7 +44667,7 @@
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y162" t="inlineStr">
@@ -44709,27 +44709,27 @@
       </c>
       <c r="AH162" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/14, 1 HR</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL162" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 14.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.6% barrel, 11.5 HR allowed</t>
         </is>
       </c>
       <c r="AM162" t="inlineStr">
@@ -44739,104 +44739,104 @@
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>24.54</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>85.08</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AQ162" t="inlineStr">
         <is>
-          <t>95.6512</t>
+          <t>96.3025</t>
         </is>
       </c>
       <c r="AR162" t="inlineStr">
         <is>
-          <t>0.2614</t>
+          <t>0.3639</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
         <is>
-          <t>0.0523</t>
+          <t>0.1029</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr">
         <is>
-          <t>0.2373</t>
+          <t>0.2969</t>
         </is>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>67.51</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>32.45</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>0.0699</t>
+          <t>0.1231</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>34.77</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>87.63</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD162" t="inlineStr">
         <is>
-          <t>0.3691</t>
+          <t>0.2747</t>
         </is>
       </c>
       <c r="BE162" t="inlineStr">
         <is>
-          <t>0.1351</t>
+          <t>0.0989</t>
         </is>
       </c>
       <c r="BF162" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="BG162" t="inlineStr"/>
       <c r="BH162" t="inlineStr"/>
       <c r="BI162" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ162" t="inlineStr"/>
@@ -50069,27 +50069,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>665953</t>
+          <t>687263</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Andres Chaparro</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-21T23:10:00Z</t>
+          <t>2026-08-22T00:15:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -50099,26 +50099,26 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Ryan Gusto</t>
+          <t>MacKenzie Gore</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>687473</t>
+          <t>669022</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>52.6</v>
+        <v>52.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -50132,26 +50132,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>51.9</v>
+        <v>46.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>48.6</v>
+        <v>46.5</v>
       </c>
       <c r="R19" t="n">
-        <v>21.5</v>
+        <v>27.6</v>
       </c>
       <c r="S19" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U19" t="n">
-        <v>63.7</v>
+        <v>50.3</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -50207,27 +50207,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.9% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 18.6 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -50237,104 +50237,104 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>12.18</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>88.45</t>
+          <t>89.74</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>101.3034</t>
+          <t>100.102</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4503</t>
+          <t>0.4166</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.2219</t>
+          <t>0.2027</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3392</t>
+          <t>0.3097</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>74.14</t>
+          <t>71.26</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>43.28</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>48.59</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>28.26</t>
+          <t>34.96</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.2279</t>
+          <t>0.1946</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>42.63</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.4257</t>
+          <t>0.3891</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1669</t>
+          <t>0.1509</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr"/>
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr"/>
@@ -50345,27 +50345,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>687952</t>
+          <t>665953</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Christian Encarnacion-Strand</t>
+          <t>Andres Chaparro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-21T23:15:00Z</t>
+          <t>2026-08-21T23:10:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -50375,17 +50375,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Ryan Gusto</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>687473</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -50408,26 +50408,26 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>62.5</v>
+        <v>51.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>35.6</v>
+        <v>48.6</v>
       </c>
       <c r="R20" t="n">
-        <v>32.1</v>
+        <v>21.5</v>
       </c>
       <c r="S20" t="n">
-        <v>81.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T20" t="n">
         <v>50</v>
       </c>
       <c r="U20" t="n">
-        <v>53.3</v>
+        <v>63.7</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -50441,7 +50441,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -50488,7 +50488,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -50503,7 +50503,7 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 20.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.9% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -50513,104 +50513,104 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>14.04</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>42.74</t>
+          <t>45.92</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>88.45</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>101.9926</t>
+          <t>101.3034</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.5177</t>
+          <t>0.4503</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.2738</t>
+          <t>0.2219</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3357</t>
+          <t>0.3392</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>73.67</t>
+          <t>74.14</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>43.28</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>48.59</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>29.79</t>
+          <t>28.26</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2279</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.3764</t>
+          <t>0.4257</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.1452</t>
+          <t>0.1669</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr"/>
       <c r="BH20" t="inlineStr"/>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -50621,27 +50621,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>687263</t>
+          <t>687952</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Christian Encarnacion-Strand</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-22T00:15:00Z</t>
+          <t>2026-08-21T23:15:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -50651,22 +50651,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MacKenzie Gore</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>669022</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -50684,26 +50684,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>46.3</v>
+        <v>62.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>46.5</v>
+        <v>35.6</v>
       </c>
       <c r="R21" t="n">
-        <v>27.6</v>
+        <v>32.1</v>
       </c>
       <c r="S21" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>46.5</v>
+        <v>53.3</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -50717,7 +50717,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -50759,7 +50759,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
@@ -50769,17 +50769,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 18.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 20.3 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -50789,104 +50789,104 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>42.74</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>89.74</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>100.102</t>
+          <t>101.9926</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4166</t>
+          <t>0.5177</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.2027</t>
+          <t>0.2738</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.3357</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>71.26</t>
+          <t>73.67</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>36.13</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>34.96</t>
+          <t>29.79</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1946</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>42.63</t>
+          <t>37.93</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.3891</t>
+          <t>0.3764</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1509</t>
+          <t>0.1452</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.85</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr"/>
       <c r="BH21" t="inlineStr"/>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
